--- a/sources/julia_step10.xlsx
+++ b/sources/julia_step10.xlsx
@@ -5039,7 +5039,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1 1 0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>0 1</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1 0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">

--- a/sources/julia_step10.xlsx
+++ b/sources/julia_step10.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD105"/>
+  <dimension ref="A1:AD106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6838,139 +6838,74 @@
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>WS+2</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>WS+2</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>3~2</t>
+          <t>– 5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tequila Sunrise</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Tequila Sunrise</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>-11</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>-11</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>-6</t>
+          <t>– Tag</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>m</t>
+          <t>24</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>Damage is 18 on the WS+2 if followed by a string starting with 1.</t>
+          <t>Only with Michelle.</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>95b94296-4b8a-4a81-a3d9-ac54f7eb3fb5</t>
+          <t>b10b068c-ac9e-49e7-81b0-86920d0c34af</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>a72aa904-1124-409f-a75b-cb6b7a95fa1f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>– 2</t>
+          <t>WS+2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WS+2 ,2</t>
+          <t>WS+2</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3~2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>– Flash Elbow</t>
+          <t>Tequila Sunrise</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tequila Sunrise – Flash Elbow</t>
+          <t>Tequila Sunrise</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6980,47 +6915,47 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>-20</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-11 -20</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>0 KD</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>-6 KD</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>15,22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -7030,49 +6965,49 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Damage is 18 on the WS+2 if followed by a string starting with 1.</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>b8c08be0-1649-4e4f-928e-d221c2f8bf81</t>
+          <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>97fbf846-d9a5-4bd3-adb7-98dc363d6569</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
+          <t>95b94296-4b8a-4a81-a3d9-ac54f7eb3fb5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>– 1,1</t>
+          <t>– 2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WS+2 ,1 ,1</t>
+          <t>WS+2 ,2</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>– Club Fist - Flash Uppercut</t>
+          <t>– Flash Elbow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tequila Sunrise – Club Fist - Flash Uppercut</t>
+          <t>Tequila Sunrise – Flash Elbow</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7082,82 +7017,67 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>-15 -14</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-11 -15 -14</t>
+          <t>-11 -20</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>-4 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>0 -4 KD</t>
+          <t>0 KD</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>-4 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>-6 -4 KD</t>
+          <t>-6 KD</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>15,5,21</t>
+          <t>15,22</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>SH</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>The uppercut does not juggle, but you can buffer in a tag.</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>16ae29bf-13c7-48a7-944e-bb7331713538</t>
+          <t>b8c08be0-1649-4e4f-928e-d221c2f8bf81</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>66ffb7fc-f605-44d7-b667-64994515726d</t>
+          <t>97fbf846-d9a5-4bd3-adb7-98dc363d6569</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -7169,27 +7089,27 @@
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>– 1,4,3</t>
+          <t>– 1,1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WS+2 ,1 ,4 ,3</t>
+          <t>WS+2 ,1 ,1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>– Club Fist - Bow - Arrow</t>
+          <t>– Club Fist - Flash Uppercut</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tequila Sunrise – Club Fist - Bow - Arrow</t>
+          <t>Tequila Sunrise – Club Fist - Flash Uppercut</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1 1 1 1</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7199,67 +7119,82 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>-15 -13 -12</t>
+          <t>-15 -14</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-11 -15 -13 -12</t>
+          <t>-11 -15 -14</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>-4 -2 KD</t>
+          <t>-4 KD</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>0 -4 -2 KD</t>
+          <t>0 -4 KD</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>-4 -2 KD</t>
+          <t>-4 KD</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>-6 -4 -2 KD</t>
+          <t>-6 -4 KD</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>5,12,15</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>26</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>15,5,12,15</t>
+          <t>15,5,21</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>mLm</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>mmLm</t>
+          <t>mmm</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>The uppercut does not juggle, but you can buffer in a tag.</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>3308856d-d15f-45c7-8281-db3de8f037ce</t>
+          <t>16ae29bf-13c7-48a7-944e-bb7331713538</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>33e320b0-7e12-4ae7-9cc4-7c606aaca590</t>
+          <t>66ffb7fc-f605-44d7-b667-64994515726d</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -7271,27 +7206,27 @@
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>– 1,4,3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WS+2 ,4</t>
+          <t>WS+2 ,1 ,4 ,3</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>– Razor Sweep</t>
+          <t>– Club Fist - Bow - Arrow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tequila Sunrise – Razor Sweep</t>
+          <t>Tequila Sunrise – Club Fist - Bow - Arrow</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1 1 1 1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7301,72 +7236,67 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-15 -13 -12</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-11 -10</t>
+          <t>-11 -15 -13 -12</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-4 -2 KD</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>0 +1</t>
+          <t>0 -4 -2 KD</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>-4 -2 KD</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>-6 +1</t>
+          <t>-6 -4 -2 KD</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5,12,15</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>32</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>15,5,12,15</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>mLm</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mmLm</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
+          <t>3308856d-d15f-45c7-8281-db3de8f037ce</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>6379a4b4-d174-412f-8409-cb6229426a50</t>
+          <t>33e320b0-7e12-4ae7-9cc4-7c606aaca590</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -7378,27 +7308,27 @@
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>–– 4</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WS+2 ,4 ,4</t>
+          <t>WS+2 ,4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>–– High Kick</t>
+          <t>– Razor Sweep</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tequila Sunrise – Razor Sweep – High Kick</t>
+          <t>Tequila Sunrise – Razor Sweep</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1 1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7408,94 +7338,99 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-11 -10 -19</t>
+          <t>-11 -10</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>0 +1 -3</t>
+          <t>0 +1</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>-6 +1 -3</t>
+          <t>-6 +1</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>15,12,23</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>mLh</t>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>90abd81b-c322-4086-ac5e-1bb4b74d0f21</t>
+          <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>96906e1d-ecb7-4784-8c38-de478dfb34ac</t>
+          <t>6379a4b4-d174-412f-8409-cb6229426a50</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
+          <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>–– d+4</t>
+          <t>–– 4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WS+2 ,4 ,d+4</t>
+          <t>WS+2 ,4 ,4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>–– Low Kick</t>
+          <t>–– High Kick</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tequila Sunrise – Razor Sweep – Low Kick</t>
+          <t>Tequila Sunrise – Razor Sweep – High Kick</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7510,72 +7445,67 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-11 -10 -14</t>
+          <t>-11 -10 -19</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>0 +1 -8</t>
+          <t>0 +1 -3</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>-6 +1 -8</t>
+          <t>-6 +1 -3</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>15,12,10</t>
+          <t>15,12,23</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>mLL</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mLh</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>8780c530-485c-4854-86c9-3d8d73cf1f42</t>
+          <t>90abd81b-c322-4086-ac5e-1bb4b74d0f21</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>feea5066-7c67-4d48-8e48-c23ce014a41a</t>
+          <t>96906e1d-ecb7-4784-8c38-de478dfb34ac</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -7587,22 +7517,22 @@
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>–– 1</t>
+          <t>–– d+4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WS+2 ,4 ,1</t>
+          <t>WS+2 ,4 ,d+4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>–– Razor's Edge</t>
+          <t>–– Low Kick</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tequila Sunrise – Razor Sweep – Razor's Edge</t>
+          <t>Tequila Sunrise – Razor Sweep – Low Kick</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7617,72 +7547,72 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-11 -10 -18</t>
+          <t>-11 -10 -14</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>0 +1 KD</t>
+          <t>0 +1 -8</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>-6 +1 KD</t>
+          <t>-6 +1 -8</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>15,12,21</t>
+          <t>15,12,10</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>mLm</t>
+          <t>mLL</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>d636b20f-0a5f-4b70-aea5-7122dee324e0</t>
+          <t>8780c530-485c-4854-86c9-3d8d73cf1f42</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>4d530135-e440-4d11-8033-58319f9a4200</t>
+          <t>feea5066-7c67-4d48-8e48-c23ce014a41a</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -7694,57 +7624,52 @@
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>b+3</t>
+          <t>–– 1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>b+3</t>
+          <t>WS+2 ,4 ,1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Liquid Sweep</t>
+          <t>–– Razor's Edge</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Liquid Sweep</t>
+          <t>Tequila Sunrise – Razor Sweep – Razor's Edge</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>27</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>-33</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-33</t>
+          <t>-11 -10 -18</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>0 +1 KD</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7754,69 +7679,74 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-6 +1 KD</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15,12,21</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>mLm</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>MS PLDc</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>081c71d9-14c8-4f81-a116-e770a0b1a68b</t>
+          <t>d636b20f-0a5f-4b70-aea5-7122dee324e0</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>49aebb0f-7e34-49a0-a13f-9792bb666e6f</t>
+          <t>4d530135-e440-4d11-8033-58319f9a4200</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>b+3</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>uf+3+4</t>
+          <t>b+3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Earthquale Stomp</t>
+          <t>Liquid Sweep</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Earthquale Stomp</t>
+          <t>Liquid Sweep</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7826,278 +7756,283 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>-33</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-32</t>
+          <t>-33</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>12</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>MS PLDc</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>841212ca-51a4-49fb-aa7a-fd658c5efc8f</t>
+          <t>081c71d9-14c8-4f81-a116-e770a0b1a68b</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>04773d5e-051d-4d43-bcc6-1676ca9c396e</t>
+          <t>49aebb0f-7e34-49a0-a13f-9792bb666e6f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>3+4</t>
+          <t>uf+3+4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3+4</t>
+          <t>uf+3+4</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Counter Clockwise Spin</t>
+          <t>Earthquale Stomp</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Counter Clockwise Spin</t>
+          <t>Earthquale Stomp</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>-32</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>-32</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Chains into Spinning Razor Kick Variations. First kick will do 20 damage.</t>
+          <t>M</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>ad154462-6148-4f1a-8a02-ea05b3eeb7b2</t>
+          <t>841212ca-51a4-49fb-aa7a-fd658c5efc8f</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>778fe738-736a-40c6-bcdb-37d9cc30283f</t>
+          <t>04773d5e-051d-4d43-bcc6-1676ca9c396e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>d+4</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>d+4</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Razor Sweep</t>
+          <t>Counter Clockwise Spin</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Razor Sweep</t>
+          <t>Counter Clockwise Spin</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>-9</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>-10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Chains into Spinning Razor Kick Variations. First kick will do 20 damage.</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
+          <t>ad154462-6148-4f1a-8a02-ea05b3eeb7b2</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>3f71e6df-2a62-4e24-83a5-cb74227d6235</t>
+          <t>778fe738-736a-40c6-bcdb-37d9cc30283f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>– N+4</t>
+          <t>d+4</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>d+4 ,N+4</t>
+          <t>d+4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>– High Kick</t>
+          <t>Razor Sweep</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Razor Sweep – High Kick</t>
+          <t>Razor Sweep</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8107,94 +8042,94 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-9 -19</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>-10 -3</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>-10 -3</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>10,23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>Lh</t>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>f3d36877-1a28-4c01-bab8-8229b80b79da</t>
+          <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>bf72a458-da43-4a73-ada1-767463f4b8b1</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
+          <t>3f71e6df-2a62-4e24-83a5-cb74227d6235</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t>– d+4</t>
+          <t>– N+4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>d+4 ,d+4</t>
+          <t>d+4 ,N+4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>– Low Kick</t>
+          <t>– High Kick</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Razor Sweep – Low Kick</t>
+          <t>Razor Sweep – High Kick</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8209,72 +8144,67 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-9 -14</t>
+          <t>-9 -19</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>-10 -8</t>
+          <t>-10 -3</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>-10 -8</t>
+          <t>-10 -3</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>10,10</t>
+          <t>10,23</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>LL</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>Lh</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>cfbeee97-432b-4263-a7e2-20492b6833aa</t>
+          <t>f3d36877-1a28-4c01-bab8-8229b80b79da</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>47df9b3a-dfe5-48f1-8c75-b3a2a221f404</t>
+          <t>bf72a458-da43-4a73-ada1-767463f4b8b1</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -8286,22 +8216,22 @@
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>– d+4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>d+4 ,1</t>
+          <t>d+4 ,d+4</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>– Razor's Edge</t>
+          <t>– Low Kick</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Razor Sweep – Razor's Edge</t>
+          <t>Razor Sweep – Low Kick</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8316,72 +8246,72 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-9 -18</t>
+          <t>-9 -14</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>-10 KD</t>
+          <t>-10 -8</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>-10 KD</t>
+          <t>-10 -8</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>10,21</t>
+          <t>10,10</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>4a44d096-425c-4067-a05d-ef151d6deb99</t>
+          <t>cfbeee97-432b-4263-a7e2-20492b6833aa</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18c62048-2b6f-46dd-8b2e-f845a8fb9287</t>
+          <t>47df9b3a-dfe5-48f1-8c75-b3a2a221f404</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -8393,22 +8323,22 @@
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>4 ,4</t>
+          <t>d+4 ,1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Spinning Razor Kicks</t>
+          <t>– Razor's Edge</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spinning Razor Kicks</t>
+          <t>Razor Sweep – Razor's Edge</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8416,111 +8346,116 @@
           <t>1 1</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>-7 -7</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-7 -7</t>
+          <t>-9 -18</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>-7 +4</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>-7 +4</t>
+          <t>-10 KD</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>KD +4</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>KD +4</t>
+          <t>-10 KD</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>20,12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>20,12</t>
+          <t>10,21</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>hL</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>hL</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
+          <t>4a44d096-425c-4067-a05d-ef151d6deb99</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>4ec9d487-7a5b-4f09-9b2e-c7316873bab2</t>
+          <t>18c62048-2b6f-46dd-8b2e-f845a8fb9287</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>4 ,4 ,4</t>
+          <t>4 ,4</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>– High Kick</t>
+          <t>Spinning Razor Kicks</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spinning Razor Kicks – High Kick</t>
+          <t>Spinning Razor Kicks</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8530,94 +8465,94 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-7 -7</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-7 -7 -19</t>
+          <t>-7 -7</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-7 +4</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>-7 +4 -3</t>
+          <t>-7 +4</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>KD +4</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>KD +4 -3</t>
+          <t>KD +4</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20,12</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>20,12,23</t>
+          <t>20,12</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>hL</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>hLh</t>
+          <t>hL</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>a5cb7052-ba1f-4451-af2a-19be86f0f2d5</t>
+          <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>7b3fbc36-00ce-49a1-81c2-c3f4245c91a3</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
+          <t>4ec9d487-7a5b-4f09-9b2e-c7316873bab2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>– d+4</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>4 ,4 ,d+4</t>
+          <t>4 ,4 ,4</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>– Low Kick</t>
+          <t>– High Kick</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spinning Razor Kicks – Low Kick</t>
+          <t>Spinning Razor Kicks – High Kick</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8632,72 +8567,67 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>-7 -7 -14</t>
+          <t>-7 -7 -19</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>-7 +4 -8</t>
+          <t>-7 +4 -3</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>KD +4 -8</t>
+          <t>KD +4 -3</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>20,12,10</t>
+          <t>20,12,23</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>hLL</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>hLh</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>a48608e8-1cd8-4504-8093-2ba46ddcf3b5</t>
+          <t>a5cb7052-ba1f-4451-af2a-19be86f0f2d5</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>f46e6f0e-0ead-4035-927a-0da05637d7bb</t>
+          <t>7b3fbc36-00ce-49a1-81c2-c3f4245c91a3</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -8709,22 +8639,22 @@
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t>– 1</t>
+          <t>– d+4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>4 ,4 ,1</t>
+          <t>4 ,4 ,d+4</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>– Razor's Edge</t>
+          <t>– Low Kick</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spinning Razor Kicks – Razor's Edge</t>
+          <t>Spinning Razor Kicks – Low Kick</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8739,72 +8669,72 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>-7 -7 -18</t>
+          <t>-7 -7 -14</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>-7 +4 KD</t>
+          <t>-7 +4 -8</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>KD +4 KD</t>
+          <t>KD +4 -8</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>20,12,21</t>
+          <t>20,12,10</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>hLm</t>
+          <t>hLL</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>e7b83a88-e3a4-4ac1-95df-1c49fb5c03d1</t>
+          <t>a48608e8-1cd8-4504-8093-2ba46ddcf3b5</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2b436f91-4f96-4547-adb6-fc94cf16ef56</t>
+          <t>f46e6f0e-0ead-4035-927a-0da05637d7bb</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -8816,57 +8746,52 @@
     <row r="90">
       <c r="B90" t="inlineStr">
         <is>
-          <t>b+4</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>b+4</t>
+          <t>4 ,4 ,1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Heaven Shatter Kick</t>
+          <t>– Razor's Edge</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Heaven Shatter Kick</t>
+          <t>Spinning Razor Kicks – Razor's Edge</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-7 -7 -18</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>-7 +4 KD</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8876,74 +8801,79 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD +4 KD</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20,12,21</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>hLm</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>CSc</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>40a9fa54-4a0b-4476-8309-5af5eb811950</t>
+          <t>e7b83a88-e3a4-4ac1-95df-1c49fb5c03d1</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>4fffe2cf-97b3-4e53-85f8-92cd71d03f6c</t>
+          <t>2b436f91-4f96-4547-adb6-fc94cf16ef56</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t>df+4&lt;2&lt;b,f+1</t>
+          <t>b+4</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>df+4 &lt;2 &lt;b,f+1</t>
+          <t>b+4</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mountain Crusher</t>
+          <t>Heaven Shatter Kick</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mountain Crusher</t>
+          <t>Heaven Shatter Kick</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1 1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8958,886 +8888,941 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>-7 -9 -15</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-7 -9 -15</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>+4 -2 KD</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>+4 -2 KD</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>+4 -2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>+4 -2 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>12,15,25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>17</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>12,15,25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>h</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>h</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>CSc</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>a5b44d75-f4c2-4bec-ac92-627e21532342</t>
+          <t>40a9fa54-4a0b-4476-8309-5af5eb811950</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>de022131-2fc1-4891-9403-47dd5f360b91</t>
+          <t>4fffe2cf-97b3-4e53-85f8-92cd71d03f6c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t>WS+4</t>
+          <t>df+4&lt;2&lt;b,f+1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WS+4</t>
+          <t>df+4 &lt;2 &lt;b,f+1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Skyscraper Kick</t>
+          <t>Mountain Crusher</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skyscraper Kick</t>
+          <t>Mountain Crusher</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 1 1</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-7 -9 -15</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-7 -9 -15</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+4 -2 KD</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+4 -2 KD</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+4 -2 KD</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+4 -2 KD</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12,15,25</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>52</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12,15,25</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mmm</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>MS</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>7439cc3f-ce60-45de-aa27-01f58633f31e</t>
+          <t>a5b44d75-f4c2-4bec-ac92-627e21532342</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>80534827-d6e9-4aa2-a626-f974adc6d519</t>
+          <t>de022131-2fc1-4891-9403-47dd5f360b91</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t>FC+df+4,3</t>
+          <t>WS+4</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FC+df+4 ,3</t>
+          <t>WS+4</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bow - Arrow</t>
+          <t>Skyscraper Kick</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bow - Arrow</t>
+          <t>Skyscraper Kick</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1 1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>-14 -14</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>-14 -14</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>-3 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>-3 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>-3 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>-3 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>12,15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>12,15</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>Lm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>f4f51a05-dcc8-4a5f-a2e8-a423c1aceae5</t>
+          <t>7439cc3f-ce60-45de-aa27-01f58633f31e</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>58440e18-0289-46f8-8663-32eb0a369a60</t>
+          <t>80534827-d6e9-4aa2-a626-f974adc6d519</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>FC+1+3</t>
+          <t>FC+df+4,3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FC+1+3</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>FC+2+4; d+1+3; d+2+4</t>
+          <t>FC+df+4 ,3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Low Parry</t>
+          <t>Bow - Arrow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Low Parry</t>
+          <t>Bow - Arrow</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1 1</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>-14 -14</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>-14 -14</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>-3 KD</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>-3 KD</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>-3 KD</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>-3 KD</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12,15</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12,15</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lm</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>378397f9-a5c6-48bc-b260-44dfff87353f</t>
+          <t>f4f51a05-dcc8-4a5f-a2e8-a423c1aceae5</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>a345769d-6667-4346-9926-12c8e2c5fa20</t>
+          <t>58440e18-0289-46f8-8663-32eb0a369a60</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
+          <t>FC+1+3</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>FC+1+3</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>FC+2+4; d+1+3; d+2+4</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Low Parry</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Low Parry</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>378397f9-a5c6-48bc-b260-44dfff87353f</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>a345769d-6667-4346-9926-12c8e2c5fa20</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
           <t>2+3+4</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>2+3+4</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Wave Taunt</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Wave Taunt</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="T96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="U96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>9acdca23-e347-4844-ac7f-41cf9fb1455f</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
+      <c r="AB96" t="inlineStr">
         <is>
           <t>83bfe4a8-8088-46fd-9d6a-08e13311a449</t>
         </is>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97">
-      <c r="A97" s="1" t="inlineStr">
-        <is>
-          <t>Unblockable Arts</t>
-        </is>
-      </c>
-    </row>
+    <row r="97"/>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
+          <t>Unblockable Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
           <t>From Stance</t>
         </is>
       </c>
-      <c r="B98" s="1" t="inlineStr">
+      <c r="B99" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="D98" s="1" t="inlineStr">
+      <c r="D99" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="E98" s="1" t="inlineStr">
+      <c r="E99" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F98" s="1" t="inlineStr">
+      <c r="F99" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr">
+      <c r="G99" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H98" s="1" t="inlineStr">
+      <c r="H99" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I98" s="1" t="inlineStr">
+      <c r="I99" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J98" s="1" t="inlineStr">
+      <c r="J99" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K98" s="1" t="inlineStr">
+      <c r="K99" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L98" s="1" t="inlineStr">
+      <c r="L99" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M98" s="1" t="inlineStr">
+      <c r="M99" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N98" s="1" t="inlineStr">
+      <c r="N99" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O98" s="1" t="inlineStr">
+      <c r="O99" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P98" s="1" t="inlineStr">
+      <c r="P99" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q98" s="1" t="inlineStr">
+      <c r="Q99" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R98" s="1" t="inlineStr">
+      <c r="R99" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S98" s="1" t="inlineStr">
+      <c r="S99" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T98" s="1" t="inlineStr">
+      <c r="T99" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U98" s="1" t="inlineStr">
+      <c r="U99" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V98" s="1" t="inlineStr">
+      <c r="V99" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W98" s="1" t="inlineStr">
+      <c r="W99" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X98" s="1" t="inlineStr">
+      <c r="X99" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y98" s="1" t="inlineStr">
+      <c r="Y99" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z98" s="1" t="inlineStr">
+      <c r="Z99" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA98" s="1" t="inlineStr">
+      <c r="AA99" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB98" s="1" t="inlineStr">
+      <c r="AB99" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC98" s="1" t="inlineStr">
+      <c r="AC99" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD98" s="1" t="inlineStr">
+      <c r="AD99" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="B99" t="inlineStr">
+    <row r="100">
+      <c r="B100" t="inlineStr">
         <is>
           <t>f+1+4</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>f+1+4</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Heaven Cannon</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Heaven Cannon</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="R100" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="AA99" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>24a1499c-dbb1-4e04-b918-cb20db832fa6</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
+      <c r="AB100" t="inlineStr">
         <is>
           <t>b4ced4c1-763a-4eb4-b61f-c12c50bd284b</t>
         </is>
       </c>
     </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>String Hit Arts</t>
-        </is>
-      </c>
-    </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
+          <t>String Hit Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
           <t>From Stance</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
+      <c r="B103" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="D102" s="1" t="inlineStr">
+      <c r="D103" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="E102" s="1" t="inlineStr">
+      <c r="E103" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F102" s="1" t="inlineStr">
+      <c r="F103" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G102" s="1" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H102" s="1" t="inlineStr">
+      <c r="H103" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I102" s="1" t="inlineStr">
+      <c r="I103" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J102" s="1" t="inlineStr">
+      <c r="J103" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K102" s="1" t="inlineStr">
+      <c r="K103" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L102" s="1" t="inlineStr">
+      <c r="L103" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M102" s="1" t="inlineStr">
+      <c r="M103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N102" s="1" t="inlineStr">
+      <c r="N103" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O102" s="1" t="inlineStr">
+      <c r="O103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P102" s="1" t="inlineStr">
+      <c r="P103" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q102" s="1" t="inlineStr">
+      <c r="Q103" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R102" s="1" t="inlineStr">
+      <c r="R103" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S102" s="1" t="inlineStr">
+      <c r="S103" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T102" s="1" t="inlineStr">
+      <c r="T103" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U102" s="1" t="inlineStr">
+      <c r="U103" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V102" s="1" t="inlineStr">
+      <c r="V103" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W102" s="1" t="inlineStr">
+      <c r="W103" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X102" s="1" t="inlineStr">
+      <c r="X103" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y102" s="1" t="inlineStr">
+      <c r="Y103" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z102" s="1" t="inlineStr">
+      <c r="Z103" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA102" s="1" t="inlineStr">
+      <c r="AA103" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB102" s="1" t="inlineStr">
+      <c r="AB103" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC102" s="1" t="inlineStr">
+      <c r="AC103" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD102" s="1" t="inlineStr">
+      <c r="AD103" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2,1,1,2,3,3,3,4,4,1</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>2 ,1 ,1 ,2 ,3 ,3 ,3 ,4 ,4 ,1</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>1 1 1 1 1 1 1 1 1 1</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>8,6,6,6,6,6,6,7,8,25</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>8,6,6,6,6,6,6,7,8,25</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>hmmhLmhhLm</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>hmmhLmhhLm</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>f26af970-57e3-45d4-baba-6711c2809508</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>ML only</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>2,1,1,2,3,3,2,3,2,1</t>
+          <t>2,1,1,2,3,3,3,4,4,1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2 ,1 ,1 ,2 ,3 ,3 ,2 ,3 ,2 ,1</t>
+          <t>2 ,1 ,1 ,2 ,3 ,3 ,3 ,4 ,4 ,1</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9847,32 +9832,32 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>8,6,6,6,6,6,7,5,5,30</t>
+          <t>8,6,6,6,6,6,6,7,8,25</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>8,6,6,6,6,6,7,5,5,30</t>
+          <t>8,6,6,6,6,6,6,7,8,25</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>hmmhLmmLm!</t>
+          <t>hmmhLmhhLm</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>hmmhLmmLm!</t>
+          <t>hmmhLmhhLm</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
+          <t>f26af970-57e3-45d4-baba-6711c2809508</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
@@ -9884,50 +9869,102 @@
     <row r="105">
       <c r="B105" t="inlineStr">
         <is>
+          <t>2,1,1,2,3,3,2,3,2,1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2 ,1 ,1 ,2 ,3 ,3 ,2 ,3 ,2 ,1</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1 1 1 1 1 1 1 1 1 1</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>8,6,6,6,6,6,7,5,5,30</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>8,6,6,6,6,6,7,5,5,30</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>hmmhLmmLm!</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>hmmhLmmLm!</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
           <t>2,1,1,2,3,3,2,1,4,3</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>2 ,1 ,1 ,2 ,3 ,3 ,2 ,1 ,4 ,3</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="Q106" t="inlineStr">
         <is>
           <t>8,6,6,6,6,67,7,10,25</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="R106" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>8,6,6,6,6,67,7,10,25</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="T106" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="U106" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
+      <c r="AB106" t="inlineStr">
         <is>
           <t>12d35c24-0209-43bc-a4fa-a6173fd493c0</t>
         </is>
       </c>
-      <c r="AD105" t="inlineStr">
+      <c r="AD106" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
